--- a/input/scripts.xlsx
+++ b/input/scripts.xlsx
@@ -56,12 +56,13 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left"/>
     </xf>
   </cellXfs>
@@ -148,7 +149,8 @@
   <commentList>
     <comment ref="A1" authorId="0" shapeId="0">
       <text>
-        <t>Nome exibido no painel. Comece com # para desativar a linha.</t>
+        <t>Nome exibido no painel. Comece com # para desativar a linha.
+Para criar uma aba nova, copie uma aba existente (botão direito na aba → Mover ou Copiar → Criar uma cópia): assim as colunas continuam em formato Texto.</t>
       </text>
     </comment>
     <comment ref="B1" authorId="0" shapeId="0">
@@ -158,7 +160,9 @@
     </comment>
     <comment ref="C1" authorId="0" shapeId="0">
       <text>
-        <t>Opcional. Texto passado ao script, ex.: --data 19/09/2026. Use aspas em caminhos com espaço. Dá para alterar no painel antes de rodar.</t>
+        <t>Opcional. Ex.: --data 19/09/2026 ou --sem-cvm.
+A coluna está em formato Texto para o Excel não transformar o que você digita (--sem-cvm em fórmula, 1/2 em data). Numa aba sem esse formato, digite um apóstrofo antes: '--sem-cvm.
+Caminho com espaço: use aspas duplas. Dá para alterar no painel antes de rodar.</t>
       </text>
     </comment>
     <comment ref="D1" authorId="0" shapeId="0">
@@ -178,7 +182,8 @@
   <commentList>
     <comment ref="A1" authorId="0" shapeId="0">
       <text>
-        <t>Nome exibido no painel. Comece com # para desativar a linha.</t>
+        <t>Nome exibido no painel. Comece com # para desativar a linha.
+Para criar uma aba nova, copie uma aba existente (botão direito na aba → Mover ou Copiar → Criar uma cópia): assim as colunas continuam em formato Texto.</t>
       </text>
     </comment>
     <comment ref="B1" authorId="0" shapeId="0">
@@ -188,7 +193,9 @@
     </comment>
     <comment ref="C1" authorId="0" shapeId="0">
       <text>
-        <t>Opcional. Texto passado ao script, ex.: --data 19/09/2026. Use aspas em caminhos com espaço. Dá para alterar no painel antes de rodar.</t>
+        <t>Opcional. Ex.: --data 19/09/2026 ou --sem-cvm.
+A coluna está em formato Texto para o Excel não transformar o que você digita (--sem-cvm em fórmula, 1/2 em data). Numa aba sem esse formato, digite um apóstrofo antes: '--sem-cvm.
+Caminho com espaço: use aspas duplas. Dá para alterar no painel antes de rodar.</t>
       </text>
     </comment>
     <comment ref="D1" authorId="0" shapeId="0">
@@ -494,28 +501,28 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
-    <col width="42" customWidth="1" min="2" max="2"/>
-    <col width="28" customWidth="1" min="3" max="3"/>
-    <col width="38" customWidth="1" min="4" max="4"/>
+    <col width="42" customWidth="1" style="1" min="2" max="2"/>
+    <col width="28" customWidth="1" style="1" min="3" max="3"/>
+    <col width="38" customWidth="1" style="1" min="4" max="4"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" s="2" t="inlineStr">
         <is>
           <t>Nome</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" s="2" t="inlineStr">
         <is>
           <t>Caminho</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" s="2" t="inlineStr">
         <is>
           <t>Argumentos</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" s="2" t="inlineStr">
         <is>
           <t>Output</t>
         </is>
@@ -527,15 +534,17 @@
           <t>Relatório de Exposição</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
+      <c r="B2" s="3" t="inlineStr">
         <is>
           <t>exposicao_html.py</t>
         </is>
       </c>
-      <c r="C2" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="D2" t="inlineStr">
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
         <is>
           <t>../output/relatorios</t>
         </is>
@@ -558,28 +567,28 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
-    <col width="42" customWidth="1" min="2" max="2"/>
-    <col width="28" customWidth="1" min="3" max="3"/>
-    <col width="38" customWidth="1" min="4" max="4"/>
+    <col width="42" customWidth="1" style="1" min="2" max="2"/>
+    <col width="28" customWidth="1" style="1" min="3" max="3"/>
+    <col width="38" customWidth="1" style="1" min="4" max="4"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" s="2" t="inlineStr">
         <is>
           <t>Nome</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" s="2" t="inlineStr">
         <is>
           <t>Caminho</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" s="2" t="inlineStr">
         <is>
           <t>Argumentos</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" s="2" t="inlineStr">
         <is>
           <t>Output</t>
         </is>
@@ -591,13 +600,13 @@
           <t>Captação</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
+      <c r="B2" s="3" t="inlineStr">
         <is>
           <t>../captacao/src/captacao.py</t>
         </is>
       </c>
-      <c r="C2" s="2" t="n"/>
-      <c r="D2" t="inlineStr">
+      <c r="C2" s="3" t="inlineStr"/>
+      <c r="D2" s="3" t="inlineStr">
         <is>
           <t>../captacao/output/captacao</t>
         </is>
